--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0106.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0106.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Nhân vật giống nhau không thể chiến đấu cùng lúc</t>
+          <t>Không thể triển khai cùng một nhân vật trong trận chiến đồng thời</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bạn không có trong danh sách bạn bè của Rover này</t>
+          <t>Cậu không có trong danh sách bạn bè của Vận Mệnh Giả này</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Chọn vật phẩm để gửi</t>
+          <t>Chọn vật phẩm để giao hàng</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chọn Nguyên liệu để đặt vào</t>
+          <t>Chọn Nguyên Liệu để bỏ vào</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Friend Request Sent</t>
+          <t>Đã Gửi Yêu Cầu Kết Bạn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Thành công</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Thành công</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Edit Name</t>
+          <t>Đổi tên</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Hồ sơ</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Thành công</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Cài đặt</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Đã bán hết</t>
+          <t>Hết hàng</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Hết Hạn</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Not Obtained/Max Limit Reached</t>
+          <t>Chưa nhận/Đã đạt giới hạn</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Signals Console</t>
+          <t>Bảng điều khiển Tín hiệu</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Matching Degree</t>
+          <t>Mức độ phù hợp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Nhận bằng cách nhấn nút theo độ dài của tần số</t>
+          <t>Nhận tín hiệu bằng cách nhấn nút theo độ dài của tần số</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Matching Degree</t>
+          <t>Mức độ phù hợp</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Tacet Field Locked</t>
+          <t>Tổ Tacet Đã Bị Khóa</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ghép cặp thành công</t>
+          <t>Ghép trận thành công</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Hết thời gian ghép cặp</t>
+          <t>Ghép trận hết thời gian</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Tacet Field đang trong Cooldown, tạm thời không thể khám phá</t>
+          <t>Tổ Tacet đang trong trạng thái nguội, tạm thời không thể khám phá</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Câu đơn</t>
+          <t>Một câu đơn</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Mô tả bản đồ Tháp Nghịch Cảnh một lần</t>
+          <t>Mô tả bản đồ Tháp Nghịch Cảnh Một Lần</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Đã bán hết</t>
+          <t>Hết hàng</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Constructing</t>
+          <t>Đang xây dựng</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nghiên cứu Failed</t>
+          <t>Nghiên cứu thất bại</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Học tập</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Đề nghị Thử thách Lại</t>
+          <t>Đề xuất Thách Đấu Lại</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Đề nghị Tiếp tục Thử thách</t>
+          <t>Đề xuất Tiếp Tục Thách Đấu</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Hệ thống</t>
+          <t>Hệ Thống</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Trưởng nhóm gửi lời mời</t>
+          <t>Trưởng đội gửi lời mời.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Hủy Theo dõi</t>
+          <t>Hủy theo dõi</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Di chuyển nhanh</t>
+          <t>Dịch chuyển nhanh</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Hiện không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Ngày tiếp theo</t>
+          <t>Ngày mai</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Resonant Tower</t>
+          <t>Tháp Cộng Hưởng</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách với tất cả thành viên trong đội còn đứng</t>
+          <t>Hoàn thành thử thách với toàn bộ thành viên đội còn đứng</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Hazard Tower</t>
+          <t>Tháp Nguy hiểm</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Echoing Tower</t>
+          <t>Tháp Vang Vọng</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Nhiệm vụ mới</t>
+          <t>Nhiệm Vụ Mới</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Triệu Tập</t>
+          <t>Triệu tập</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Chạm vào bất kỳ đâu để tiếp tục</t>
+          <t>Nhấn bất kỳ đâu để tiến hành</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Chạm vào bất kỳ đâu để tiếp tục</t>
+          <t>Nhấn bất kỳ đâu để tiến hành</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Tháo trang bị</t>
+          <t>Tháo Trang Bị</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Thư chưa đọc</t>
+          <t>Thư Chưa Đọc</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Vật phẩm đang trong thời gian Cooldown</t>
+          <t>Vật phẩm đang hồi</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Vật phẩm này chỉ dành cho Resonator bị hạ gục</t>
+          <t>Vật phẩm này chỉ dành cho Resonator bị đánh gục.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Sử dụng vật phẩm hồi sinh</t>
+          <t>Dùng vật phẩm hồi sinh</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Kuro User Agreement</t>
+          <t>Thỏa thuận sử dụng Kuro</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Không đủ nguyên liệu Thăng hoa</t>
+          <t>Vật liệu Thăng Hoa không đủ</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Không đủ tiền tệ để Thăng hoa</t>
+          <t>Không đủ tiền tệ để Tiến Hóa</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Syntonize</t>
+          <t>Điều tần</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn kinh nghiệm, không thể thêm nữa</t>
+          <t>Đã đạt giới hạn kinh nghiệm, không thể bổ sung thêm.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Crafting</t>
+          <t>Đang chế tác</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Khe đầy</t>
+          <t>Đã đầy khe</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Đã nâng cấp</t>
+          <t>đã nâng cấp</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Syntonized</t>
+          <t>Đã điều tần</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Enhanced</t>
+          <t>Đã Nâng cấp</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Craft</t>
+          <t>Chế Tạo</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Weapon Materials</t>
+          <t>Vật Liệu Vũ Khí</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Vật liệu nâng cấp không đủ</t>
+          <t>Vật liệu nâng cấp không đủ.</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Sụp đổ</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>So sánh</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Vật liệu Syntonize không đủ</t>
+          <t>Không đủ nguyên liệu Đồng Điệu</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Shell Credit không đủ để Syntonize</t>
+          <t>Tín dụng Vỏ sò không đủ để Đồng điệu</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Syntonize</t>
+          <t>Điều tần</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Chọn vật liệu</t>
+          <t>Chọn nguyên liệu</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Vật liệu nâng cấp không đủ</t>
+          <t>Vật liệu nâng cấp không đủ.</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Giai đoạn SOL3 thấp hơn</t>
+          <t>Giảm Giai Đoạn SOL3</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Đặt lại giai đoạn SOL3</t>
+          <t>Đặt lại Pha SOL3</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Giai đoạn SOL3</t>
+          <t>Giai Đoạn SOL3</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Yesterday</t>
+          <t>Hôm qua</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Cannot Merge Enhanced Echoes</t>
+          <t>Không thể Hợp Nhất Tiếng Vọng Cường Hóa</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Vui lòng đặt vào 5 Echo</t>
+          <t>Hãy đặt vào 5 Echo.</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Đã đạt số lượng tối đa</t>
+          <t>Đã đạt giới hạn số lượng</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Quick Selection</t>
+          <t>Lựa Chọn Nhanh</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Vui lòng chọn ít nhất 5 Echo</t>
+          <t>Hãy chọn ít nhất 5 Echo nhé.</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Tạo hồ sơ người chơi thất bại</t>
+          <t>Tạo hồ sơ Vận Mệnh Giả thất bại</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Re-login</t>
+          <t>Đăng Nhập Lại</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Đã tiêu hao vật phẩm trùng lặp, vui lòng thử lại</t>
+          <t>Tiêu thụ vật phẩm trùng lặp, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Đã tiêu hao vật phẩm trùng lặp, vui lòng thử lại</t>
+          <t>Tiêu thụ vật phẩm trùng lặp, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Lỗi tiêu hao vật phẩm, vui lòng thử lại</t>
+          <t>Lỗi tiêu thụ vật phẩm, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Tiêu hao Echo không có kinh nghiệm, vui lòng thử lại</t>
+          <t>Echo không có kinh nghiệm, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Lỗi khe Tuning, vui lòng thử lại</t>
+          <t>Lỗi khe điều chỉnh, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Có kết quả Tuning chưa xác nhận</t>
+          <t>Có kết quả Điều Tần chưa được xác nhận</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Tiêu hao vật phẩm sai chất lượng, vui lòng thử lại</t>
+          <t>Vật phẩm không đúng chất lượng, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Tuning EXP không đủ</t>
+          <t>Kinh Nghiệm Điều Chỉnh Không Đủ</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Không có Echo cùng tên được đặt vào, vui lòng thử lại</t>
+          <t>Echo trùng tên rồi, thử lại đi</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Không có Tuning để xác nhận</t>
+          <t>Chưa xác nhận Tần số nào</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Nhân vật hiện tại không thể kích hoạt kỹ năng đặc biệt, vui lòng thử lại</t>
+          <t>Nhân vật hiện tại không thể kích hoạt kỹ năng đặc biệt, hãy thử lại</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Echo hiện tại chưa được trang bị, vui lòng thử lại</t>
+          <t>Echo hiện tại chưa được trang bị, hãy thử lại.</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Echo hiện tại không có kỹ năng để kích hoạt</t>
+          <t>Echo hiện tại không có kỹ năng để kích hoạt.</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Cấu hình thuộc tính Echo Tuning không tồn tại, vui lòng thử lại</t>
+          <t>Không tìm thấy cấu hình thuộc tính Điều Chỉnh Tiếng Vọng, hãy thử lại</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tạo Mainstat cho Echo thất bại, vui lòng thử lại</t>
+          <t>Tạo Chỉ Số Chính Thất Bại, Vui Lòng Thử Lại</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Chức năng Điểm Hoạt Động chưa được mở</t>
+          <t>Chức năng Điểm Hoạt Động chưa mở</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Điểm Hoạt Động chưa được nhận</t>
+          <t>Chưa nhận nhiệm vụ Điểm Hoạt Động</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Tiêu hao quá nhiều vật phẩm khi nâng cấp vũ khí, vui lòng thử lại</t>
+          <t>Tiêu hao quá nhiều vật phẩm khi nâng cấp vũ khí, hãy thử lại.</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Lỗi tiêu hao vật liệu</t>
+          <t>Lỗi tiêu thụ nguyên liệu</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Vật phẩm không tồn tại, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức nếu có thắc mắc</t>
+          <t>Vật phẩm không tồn tại, nếu có thắc mắc hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Vật phẩm không tồn tại, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức nếu có thắc mắc</t>
+          <t>Vật phẩm không tồn tại, nếu có thắc mắc hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Vật phẩm đã bị khóa</t>
+          <t>Vật phẩm đang bị khóa</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Tiêu hao vật phẩm trùng lặp</t>
+          <t>Tiêu thụ vật phẩm trùng lặp</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Vũ khí đã được trang bị</t>
+          <t>Vũ khí đã được trang bị.</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Tiêu hao vật phẩm trùng lặp</t>
+          <t>Tiêu thụ vật phẩm trùng lặp</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Kinh nghiệm nâng cấp không đủ, vui lòng thử lại</t>
+          <t>Kinh nghiệm nâng cấp không đủ, vui lòng thử lại.</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện nâng cấp, vui lòng thử lại</t>
+          <t>Chưa đủ điều kiện nâng cấp, hãy thử lại.</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Chỉ số chính của Echo không khớp, vui lòng thử lại</t>
+          <t>Chỉ số chính của Echo không khớp, hãy thử lại</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Chỉ số phụ của Echo không khớp, vui lòng thử lại</t>
+          <t>Chỉ số phụ của Echo không khớp, hãy thử lại</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Chức năng thử thách Tháp Nghịch Cảnh chưa mở</t>
+          <t>Chức năng thử thách Tháp Thử Thách chưa mở</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Hiện không trong thử thách Tháp Nghịch Cảnh</t>
+          <t>Hiện không tham gia thử thách Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Thử thách Tháp Nghịch Cảnh hiện tại chưa mở</t>
+          <t>Thử thách Tháp Nghịch Cảnh hiện chưa mở.</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Giá trị mệt mỏi của Resonator không đủ</t>
+          <t>Resonator đã kiệt sức, không thể tiếp tục</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Chưa vượt qua tầng trước của Tháp Nghịch Cảnh, vui lòng thử lại</t>
+          <t>Bạn chưa vượt qua tầng khởi động của Tháp Thử Thách, hãy thử lại</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Chưa vượt qua tầng trước của Tháp Nghịch Cảnh, vui lòng thử lại</t>
+          <t>Bạn chưa vượt qua tầng khởi động của Tháp Thử Thách, hãy thử lại</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Chưa vượt qua tầng trước của Tháp Nghịch Cảnh, vui lòng thử lại</t>
+          <t>Bạn chưa vượt qua tầng khởi động của Tháp Thử Thách, hãy thử lại</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Chu kỳ Tháp Nghịch Cảnh hiện tại đã được làm mới</t>
+          <t>Chu kỳ Tháp Nghịch Cảnh hiện đã được làm mới.</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Thử thách Holographic: Calamity đã mở</t>
+          <t>Thử thách Hologram: Tận Thế đã mở</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Thử thách Holographic: Calamity chưa mở khóa</t>
+          <t>Thử thách Hologram: Tận Thế chưa được mở khóa</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thử thách Holographic: Calamity chưa mở</t>
+          <t>Thử thách Hologram: Tận Thế chưa mở</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Chỉ số phụ của Echo chưa mở khóa, vui lòng thử lại sau</t>
+          <t>Chỉ số phụ của Echo chưa mở khóa, hãy thử lại sau</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Cấu hình tiêu hao Echo bị lỗi, vui lòng thử lại sau</t>
+          <t>Cấu hình tiêu hao của Echo bị lỗi, hãy thử lại sau</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Không có dữ liệu khả dụng, vui lòng mở khóa ít nhất một Echo tương ứng trước</t>
+          <t>Không có dữ liệu, hãy mở khóa ít nhất một Echo tương ứng trước</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Phân giải địa chỉ mạng thất bại, vui lòng khởi động lại mạng và thử lại</t>
+          <t>Không thể phân giải địa chỉ mạng, vui lòng khởi động lại mạng và thử lại</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Hủy vật phẩm bị trùng lặp, vui lòng thử lại</t>
+          <t>Đã phá hủy vật phẩm nhiều lần, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Chứa vật phẩm không thể hủy</t>
+          <t>Chứa vật phẩm không thể phá hủy</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Chứa vật phẩm không thể hủy</t>
+          <t>Chứa vật phẩm không thể phá hủy</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Chứa vật phẩm không thể bị phá hủy</t>
+          <t>Chứa vật phẩm không thể phá hủy</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Chứa vật phẩm không thể bị phá hủy</t>
+          <t>Chứa vật phẩm không thể phá hủy</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Chứa vật phẩm không thể bị phá hủy</t>
+          <t>Chứa vật phẩm không thể phá hủy</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Không thể kết nối với máy chủ</t>
+          <t>Không thể kết nối với chủ phòng</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Không thể tham gia Chơi cùng khi đã bị đánh bại</t>
+          <t>Không thể tham gia Hợp Tác khi đã bị đánh bại</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Chủ phòng đang ở trạng thái tử trận và tạm thời không thể vào</t>
+          <t>Chủ nhân đang ở trạng thái tử vong, không thể truy cập tạm thời</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Đang tải cảnh, tạm thời không thể rời đi</t>
+          <t>Đang tải cảnh, không thể rời đi tạm thời</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Số lượng người chơi không đủ để tái chiến</t>
+          <t>Số người chơi không đủ để tái thử thách.</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Có người chơi đang rời đi, không thể tái chiến</t>
+          <t>Có người chơi đã rời đi, không thể thách đấu lại</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Người chơi hiện tại chưa bị hạ gục, không thể tái chiến</t>
+          <t>Người chơi hiện tại chưa bị hạ gục, không thể tái thách đấu</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Chưa giải quyết xong, không thể yêu cầu tái đấu</t>
+          <t>Bồn chồn, không thể tái chiến</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Không thể chấp nhận lời mời nhiều lần</t>
+          <t>Không thể chấp nhận lời mời nhiều lần liên tiếp</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Người chơi hiện tại không phải chủ phòng, không thể gửi lời mời</t>
+          <t>Ngươi không phải chủ phòng, không thể gửi lời mời</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Chủ phòng chưa khởi động tái chiến</t>
+          <t>Chủ trì chưa khởi động trận đấu lại.</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Đã xảy ra bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Đã xảy ra bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Đã xảy ra bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Đã xảy ra bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Đã xảy ra bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Đang xin vào, không thể thao tác lặp lại</t>
+          <t>Đang đăng ký tham gia, không thể lặp lại thao tác</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Đang truy vấn thông tin bạn bè, không thể thao tác lặp lại</t>
+          <t>Đang truy vấn thông tin bạn bè, không thể lặp lại thao tác</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Đang truy vấn thông tin người chơi, không thể thao tác lặp lại</t>
+          <t>Đang truy vấn thông tin người chơi, không thể lặp lại thao tác</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Không thể sử dụng chức năng dịch chuyển trong quá trình tải, vui lòng thử lại sau</t>
+          <t>Không thể sử dụng chức năng dịch chuyển trong quá trình tải, hãy thử lại sau</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Không thể lặp lại quá trình dịch chuyển, vui lòng thử lại sau</t>
+          <t>Không thể lặp lại quá trình dịch chuyển, hãy thử lại sau</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Có lỗi xảy ra trong quá trình dịch chuyển, vui lòng thử lại sau</t>
+          <t>Có dị thường trong dịch chuyển, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Người chơi đang dịch chuyển, không thể thực hiện thao tác hiện tại</t>
+          <t>Người chơi đang dịch chuyển, không thể thực hiện thao tác này</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Có người chơi trong đội đang dịch chuyển, không thể giải tán</t>
+          <t>Có một người chơi trong đội đang dịch chuyển, không thể giải tán đội.</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Bạn không thể gửi yêu cầu Hợp tác trong lúc dịch chuyển</t>
+          <t>Không thể gửi yêu cầu Hợp Tác trong khi dịch chuyển</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Không tìm thấy nội dung gửi của email, vui lòng thử lại sau</t>
+          <t>Không tìm thấy tên người gửi email, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Kết nối thất bại, vui lòng đăng nhập lại</t>
+          <t>Kết nối lại thất bại, vui lòng đăng nhập lại.</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Bạn không thể xin tham gia thế giới của người khác trong khi đang ghép trận, vui lòng thử lại sau</t>
+          <t>Bạn không thể xin tham gia thế giới của người khác khi đang ghép trận, hãy thử lại sau.</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Bạn không thể tham gia khi đang trong cốt truyện, vui lòng thử lại sau</t>
+          <t>Bạn không thể tham gia khi đang trong cốt truyện, hãy thử lại sau nhé.</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Bạn không thể tham gia khi chủ thế giới đang trong cốt truyện, vui lòng thử lại sau</t>
+          <t>Bạn không thể tham gia khi chủ thế giới đang trong cốt truyện, hãy thử lại sau.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Mục thành tựu đã hoàn thành</t>
+          <t>Đã hoàn thành mục thành tựu</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Danh sách hiển thị của Resonator Showcase đã vượt quá giá trị tối đa</t>
+          <t>Danh sách trưng bày của Resonator Showcase đã vượt quá giới hạn tối đa</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Danh sách hiển thị của Resonator Showcase không thể để trống</t>
+          <t>Danh sách trưng bày của Resonator Showcase không thể để trống</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Hết thời gian kết nối mạng, vui lòng thử lại</t>
+          <t>Kết nối mạng hết thời gian chờ, vui lòng thử lại</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Hệ thống Thành tựu chưa được kích hoạt</t>
+          <t>Hệ thống thành tựu chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Hiện không còn Ẩn ngữ nào khả dụng trong Khu Vực Ký ức này</t>
+          <t>Trong Vùng Ký Ức này hiện không có Ẩn Dụ nào khác</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Điểm dịch chuyển không tồn tại</t>
+          <t>Điểm Dẫn Đường không tồn tại</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Không thể mở bảng điều khiển này trong Chế độ Hợp tác</t>
+          <t>Không thể mở bảng điều khiển này trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đã phát hiện bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Có lỗi bất thường, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ khách hàng chính thức</t>
+          <t>Có dị thường, nếu có thắc mắc, hãy liên hệ bộ phận hỗ trợ chính thức</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Test gửi tự động mẫu</t>
+          <t>Kiểm tra gửi tự động mẫu</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Test gửi tự động mẫu</t>
+          <t>Kiểm tra gửi tự động mẫu</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Không context</t>
+          <t>Không có ngữ cảnh.</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Hành vi của máy trạng thái chỉ có thể thực thi một lần</t>
+          <t>Hành vi máy trạng thái chỉ có thể thực thi một lần</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Montage không tồn tại</t>
+          <t>Đoạn phim này không tồn tại</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Montage không chứa đạn</t>
+          <t>Đoạn phim không chứa viên đạn nào</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Montage không thể tạo hành vi tiếp theo</t>
+          <t>Đoạn phim dựng không thể tạo hành vi tiếp theo</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Tham số useSkillInfo bị trống</t>
+          <t>Tham số useSkillInfo bị null</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Hiện không ở trạng thái trực tuyến, vui lòng thử lại sau</t>
+          <t>Hiện không trực tuyến, hãy thử lại sau</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Không Đội Members Now</t>
+          <t>Chưa có thành viên nào trong đội</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Người chơi không có thông tin đội đấu, vui lòng thử lại sau</t>
+          <t>Người chơi không có thông tin trận đấu đội, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Đội đấu của chủ phòng không có thành viên, vui lòng thử lại sau</t>
+          <t>Đội thi đấu của chủ nhân chưa có thành viên nào, hãy thử lại sau nhé</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Người chơi không ở trong đội đấu, vui lòng thử lại sau</t>
+          <t>Người chơi không có trong đội hình trận đấu, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Đội đấu đã đầy</t>
+          <t>Đội ghép trận đã đủ người.</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nhóm thử thách đồng đội không có quyền, vui lòng thử lại sau</t>
+          <t>Đội thách đấu không có quyền tham gia, hãy thử lại sau.</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Người chơi đã ở trong nhóm thử thách đồng đội, vui lòng thử lại sau</t>
+          <t>Người chơi đã ở trong đội thử thách, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Cảnh hiện tại của người chơi trống, vui lòng cập nhật và thử lại</t>
+          <t>Cảnh hiện tại của người chơi trống rỗng, vui lòng cập nhật và thử lại</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Danh sách nhân vật trong cảnh của người chơi trống, vui lòng cập nhật và thử lại</t>
+          <t>Danh sách nhân vật trong cảnh của người chơi trống rỗng, vui lòng cập nhật và thử lại</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Resonator cần chuyển không có trong đội hiện tại</t>
+          <t>Resonator cần thay không có trong đội hiện tại.</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng cấp Ngân Hàng Dữ Liệu</t>
+          <t>Đã nhận phần thưởng cấp độ Cơ sở dữ liệu.</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Tải dữ liệu hệ thống bạn bè thất bại</t>
+          <t>Không tải được dữ liệu hệ thống bạn bè</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Bạn chưa nhận được Giấy Phép Sử Dụng tiện ích này ở khu vực hiện tại</t>
+          <t>Bạn chưa có Giấy Phép Sử Dụng tiện ích này ở khu vực hiện tại.</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Đã xảy ra lỗi, nếu có thắc mắc, vui lòng liên hệ bộ phận hỗ trợ chính thức</t>
+          <t>Đã xảy ra lỗi, nếu có thắc mắc gì, hãy liên hệ bộ phận hỗ trợ chính thức.</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mua</t>
+          <t>Chưa đủ điều kiện mua</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Các mục trên đã hết hạn</t>
+          <t>Các vật phẩm trên đã hết hạn sử dụng.</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Chọn mục để xóa</t>
+          <t>Chọn vật phẩm để loại bỏ</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Bạn không thể chọn thêm mục</t>
+          <t>Bạn không thể chọn thêm vật phẩm</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Vật phẩm Obtained</t>
+          <t>Đã nhận được vật phẩm</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Vui lòng chọn mục để xóa</t>
+          <t>Hãy chọn vật phẩm cần loại bỏ</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hãy hồi sinh Resonator hiện tại trước khi tham gia Co-op</t>
+          <t>Hãy hồi sinh Resonator hiện tại trước khi tham gia Chơi cùng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Hãy hồi sinh Resonator hiện tại trước khi tham gia Co-op</t>
+          <t>Hãy hồi sinh Resonator hiện tại trước khi tham gia Chơi cùng</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Hãy hồi sinh Resonator hiện tại trước khi tham gia Co-op</t>
+          <t>Hãy hồi sinh Resonator hiện tại trước khi tham gia Chơi cùng</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Nhiệm vụ mới có sẵn</t>
+          <t>Nhiệm Vụ Mới đã xuất hiện</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Sent</t>
+          <t>Đã gửi</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Received</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 17</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 17</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>COST 1</t>
+          <t>CHI PHÍ 1</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>COST 3</t>
+          <t>CHI PHÍ 3</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>COST 4</t>
+          <t>CHI PHÍ 4</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Phó bản sự kiện này chưa mở</t>
+          <t>Vùng sự kiện này chưa mở khóa</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 30</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Hoàn thành Độ khó IV để mở khóa</t>
+          <t>Hoàn thành Độ Khó IV để mở khóa</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Hoàn thành Độ khó II để mở khóa</t>
+          <t>Hoàn thành Độ Khó II để mở khóa</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Khảo sát Khám phá Hương Trấn đã được làm mới</t>
+          <t>Nhiệm Vụ Khảo Sát của Thám Hiểm Vực Gió đã được làm mới</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Tính năng chưa khả dụng</t>
+          <t>Chức năng không khả dụng</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Tính năng Bộ sưu tập Ký ức chưa mở khóa</t>
+          <t>Chức năng Bộ Sưu Tập Ký Ức chưa mở khóa</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Dữ liệu sự kiện lỗi, vui lòng thử lại sau</t>
+          <t>Dữ liệu sự kiện bị lỗi, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Dữ liệu sự kiện lỗi</t>
+          <t>Dữ liệu sự kiện bị lỗi</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Bạn đã nhận thưởng nhiệm vụ</t>
+          <t>Ngươi đã nhận phần thưởng nhiệm vụ rồi</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Bạn đã nhận thưởng sự kiện</t>
+          <t>Ngươi đã nhận phần thưởng sự kiện rồi</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Không thể nhận thưởng</t>
+          <t>Không thể nhận phần thưởng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Đang đổi thưởng, vui lòng thử lại sau</t>
+          <t>Đang đổi, vui lòng thử lại sau</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Giai đoạn này đã bị khóa</t>
+          <t>Giai đoạn này đã bị khóa.</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Sự kiện đã kết thúc</t>
+          <t>Sự kiện đã kết thúc.</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Vui lòng hoàn thành nhiệm vụ tiên quyết</t>
+          <t>Hãy hoàn thành nhiệm vụ tiên quyết trước</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn chọn meme</t>
+          <t>Đã đạt giới hạn chọn Memes</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Nhân vật dùng thử không khả dụng</t>
+          <t>Nhân vật thử nghiệm không khả dụng</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đơn hàng của bạn đã được hoàn tiền</t>
+          <t>Đơn hàng của cậu đã được hoàn trả</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Giao dịch của bạn chưa hoàn tất</t>
+          <t>Giao dịch của cậu chưa hoàn tất.</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Yêu cầu hoàn tiền của bạn không thể được chấp thuận</t>
+          <t>Yêu cầu hoàn tiền của cậu không được chấp thuận.</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Vật phẩm này đã bị khóa</t>
+          <t>Vật phẩm này đang bị khóa.</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Bạn chưa đáp ứng điều kiện mua vật phẩm này</t>
+          <t>Cậu chưa đạt đủ điều kiện mua vật phẩm này</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Điểm đánh dấu dò tìm Vật phẩm không tồn tại</t>
+          <t>Không tồn tại điểm đánh dấu Phát Hiện cho Vật Tư</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Điểm đánh dấu Vật phẩm không tồn tại</t>
+          <t>Điểm đánh dấu vật tư không tồn tại</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Điểm đánh dấu dò tìm Vật phẩm đã tồn tại</t>
+          <t>Đã tồn tại điểm đánh dấu Phát Hiện cho Vật Tư</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Không thể vào Sonoro Sphere với Nhân vật dùng thử</t>
+          <t>Không thể vào Sonoro Sphere với Nhân Vật Thử Nghiệm</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Vui lòng liên hệ Bộ phận Chăm sóc Khách hàng để được hỗ trợ</t>
+          <t>Hãy liên hệ với Dịch vụ Khách hàng của chúng tôi để được hỗ trợ.</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Phần thưởng đã được nhận</t>
+          <t>Đã nhận phần thưởng</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Insufficient Adventure Logs</t>
+          <t>Nhật Ký Phiêu Lưu không đủ</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu</t>
+          <t>Sự kiện chưa bắt đầu.</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 5 hoặc ghé thăm Nhà hàng Panhua trong Chương 4</t>
+          <t>Đạt Cấp Độ Liên Minh 5 hoặc ghé thăm Nhà hàng Panhua trong Chương 4</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 15 hoặc hoàn thành Nhiệm vụ Chính "Kiếm Khách Đối Đầu"</t>
+          <t>Đạt Cấp Độ Liên Minh 15 hoặc hoàn thành Nhiệm Vụ Chính "Kiếm Kích Tranh Phong"</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên minh 14</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương I Chương VI để mở khóa</t>
+          <t>Hoàn thành Chương I Cảnh VI để mở khóa</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 16 và hoàn thành Chương I Chương III</t>
+          <t>Đạt Cấp Độ Liên Minh 16 và hoàn thành Chương I Hồi III</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Thăng cấp Resonator</t>
+          <t>Thăng Cấp Resonator</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Cấp Độ SOL3 Giai đoạn</t>
+          <t>Cấp Độ Pha SOL3</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Mode Switch</t>
+          <t>Chuyển Đổi Chế Độ</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Remove Patches</t>
+          <t>Gỡ Bản Vá</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Tiến độ Nhiệm vụ</t>
+          <t>Tiến độ nhiệm vụ</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính Chương VII "Thời Khắc Tan Băng" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính Chương VII "Thaw of Eons" để mở khóa</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 18 và hoàn thành Nhiệm vụ Chính Chương VI "Bão Chiến Vĩ Đại" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 18 và hoàn thành Hồi VI "Cuồng Phong Đại Chiến" của Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính Chương I Chương VI "Bão Chiến Vĩ Đại"</t>
+          <t>Hoàn thành Chương VI "Bão Chiến Kinh Hoàng" của Chương I Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 18</t>
+          <t>Đạt Cấp Độ Liên Minh 18</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Vui lòng nhập ID Người dùng</t>
+          <t>Vui lòng nhập ID Người Dùng</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Moments: Chixia</t>
+          <t>Khoảnh khắc: Chixia</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Moments: Encore</t>
+          <t>Khoảnh Khắc: Encore</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Moments: Changli</t>
+          <t>Khoảnh khắc: Changli</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Moments: Yangyang</t>
+          <t>Khoảnh Khắc: Yangyang</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Moments: Lingyang</t>
+          <t>Khoảnh Khắc: Lingyang</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Moments: Jianxin</t>
+          <t>Khoảnh Khắc: Jianxin</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Moments: Sanhua</t>
+          <t>Khoảnh Khắc: Sanhua</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Moments: Jiyan</t>
+          <t>Khoảnh Khắc: Jiyan</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Moments: Yinlin</t>
+          <t>Khoảnh Khắc: Yinlin</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Moments: Zhezhi</t>
+          <t>Khoảnh Khắc: Zhezhi</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Moments: Jinhsi</t>
+          <t>Khoảnh Khắc: Jinhsi</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Đạt xếp hạng SS hoặc cao hơn cho bất kỳ Wish nào</t>
+          <t>Đạt xếp hạng SS hoặc cao hơn cho bất kỳ Điều Ước nào</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Độ nổi tiếng trong lễ hội Moon-Chasing</t>
+          <t>Đạt 2.000 Độ Nổi Tiếng trong lễ hội Moon-Chasing</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Đạt 6.000 Độ nổi tiếng trong lễ hội Moon-Chasing</t>
+          <t>Đạt 6.000 Độ Nổi Tiếng trong Lễ Hội Đuổi Trăng</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Đạt 20.000 Độ nổi tiếng trong lễ hội Moon-Chasing</t>
+          <t>Đạt 20.000 Độ Phổ Biến trong Lễ Hội Đuổi Trăng</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
